--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>121344591</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>121344590</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -945,16 +945,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -964,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R4" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,17 +985,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1069,7 +1065,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R5" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,22 +1114,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +945,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R4" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,22 +994,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,16 +1069,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R5" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1114,17 +1109,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,16 +945,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -964,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R4" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,17 +985,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,7 +1065,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R5" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,22 +1114,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>121344590</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>121344591</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -945,7 +945,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R4" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,22 +994,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1065,16 +1069,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R5" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1114,17 +1109,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,16 +945,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -964,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R4" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,17 +985,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,7 +1065,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R5" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,22 +1114,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +945,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R4" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,22 +994,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,16 +1069,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R5" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1114,17 +1109,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -945,16 +945,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -964,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R4" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,17 +985,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1069,7 +1065,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1079,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R5" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,22 +1114,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344590</v>
+        <v>121344591</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -945,7 +945,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377563</v>
+        <v>377406</v>
       </c>
       <c r="R4" t="n">
-        <v>6615234</v>
+        <v>6615079</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,22 +994,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0843</t>
+          <t>S-Arv-0842</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Knärot intill liggande låga av tall.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344591</v>
+        <v>121344590</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1065,16 +1069,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1084,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377406</v>
+        <v>377563</v>
       </c>
       <c r="R5" t="n">
-        <v>6615079</v>
+        <v>6615234</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1114,17 +1109,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>S-Arv-0842</t>
+          <t>S-Arv-0843</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Knärot intill liggande låga av tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14030-2024 artfynd.xlsx
+++ b/artfynd/A 14030-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>121344591</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>121344590</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
